--- a/toeic-test-v5/trial1_v2.xlsx
+++ b/toeic-test-v5/trial1_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63381E74-2A69-43CD-8107-4DD2141AC884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8831D29E-A663-4269-A63F-1B6A30CE9B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="165" yWindow="780" windowWidth="15225" windowHeight="13875" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-45" yWindow="1185" windowWidth="15225" windowHeight="13875" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="12">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -493,14 +493,14 @@
       </c>
       <c r="C6">
         <f>SUM(listening!C73:C102)</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>30</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8" spans="2:5">
@@ -555,14 +555,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.1875</v>
+        <v>0.39583333333333331</v>
       </c>
     </row>
   </sheetData>
@@ -579,7 +579,7 @@
     <row r="1" spans="1:4">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1073,53 +1073,107 @@
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
+      <c r="B82" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
         <f t="shared" si="1"/>
         <v>81</v>
       </c>
+      <c r="B83" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
         <f t="shared" si="1"/>
         <v>82</v>
       </c>
+      <c r="B84" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
         <f t="shared" si="1"/>
         <v>83</v>
       </c>
+      <c r="B85" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85">
+        <v>1</v>
+      </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
         <f t="shared" si="1"/>
         <v>84</v>
       </c>
+      <c r="B86" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
         <f t="shared" si="1"/>
         <v>85</v>
       </c>
+      <c r="B87" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87">
+        <v>1</v>
+      </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
         <f t="shared" si="1"/>
         <v>86</v>
       </c>
+      <c r="B88" t="s">
+        <v>5</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
         <f t="shared" si="1"/>
         <v>87</v>
       </c>
+      <c r="B89" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89">
+        <v>0</v>
+      </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
         <f t="shared" si="1"/>
         <v>88</v>
+      </c>
+      <c r="B90" t="s">
+        <v>5</v>
+      </c>
+      <c r="C90">
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1280,7 +1334,7 @@
     <row r="1" spans="1:4">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1781,59 +1835,119 @@
         <f t="shared" si="1"/>
         <v>181</v>
       </c>
+      <c r="B83" t="s">
+        <v>4</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
         <f t="shared" si="1"/>
         <v>182</v>
       </c>
+      <c r="B84" t="s">
+        <v>5</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
         <f t="shared" si="1"/>
         <v>183</v>
       </c>
+      <c r="B85" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85">
+        <v>1</v>
+      </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
         <f t="shared" si="1"/>
         <v>184</v>
       </c>
+      <c r="B86" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86">
+        <v>1</v>
+      </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
         <f t="shared" si="1"/>
         <v>185</v>
       </c>
+      <c r="B87" t="s">
+        <v>4</v>
+      </c>
+      <c r="C87">
+        <v>1</v>
+      </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
         <f t="shared" si="1"/>
         <v>186</v>
       </c>
+      <c r="B88" t="s">
+        <v>4</v>
+      </c>
+      <c r="C88">
+        <v>1</v>
+      </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
         <f t="shared" si="1"/>
         <v>187</v>
       </c>
+      <c r="B89" t="s">
+        <v>5</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
         <f t="shared" si="1"/>
         <v>188</v>
       </c>
+      <c r="B90" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90">
+        <v>1</v>
+      </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
         <f t="shared" si="1"/>
         <v>189</v>
       </c>
+      <c r="B91" t="s">
+        <v>5</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
         <f t="shared" si="1"/>
         <v>190</v>
+      </c>
+      <c r="B92" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:3">

--- a/toeic-test-v5/trial1_v2.xlsx
+++ b/toeic-test-v5/trial1_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8831D29E-A663-4269-A63F-1B6A30CE9B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{324571E1-69F5-4B88-BB2B-4416E514F8C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-45" yWindow="1185" windowWidth="15225" windowHeight="13875" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2055" yWindow="540" windowWidth="15225" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="12">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -493,14 +493,14 @@
       </c>
       <c r="C6">
         <f>SUM(listening!C73:C102)</f>
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D6">
         <v>30</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8" spans="2:5">
@@ -539,14 +539,14 @@
       </c>
       <c r="C10">
         <f>SUM(reading!C43:C54)</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D10">
         <v>12</v>
       </c>
       <c r="E10" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.91666666666666663</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -579,7 +579,7 @@
     <row r="1" spans="1:4">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -966,106 +966,160 @@
         <v>62</v>
       </c>
     </row>
-    <row r="65" spans="1:1">
+    <row r="65" spans="1:3">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
     </row>
-    <row r="66" spans="1:1">
+    <row r="66" spans="1:3">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
+    <row r="67" spans="1:3">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
+    <row r="68" spans="1:3">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="1:1">
+    <row r="69" spans="1:3">
       <c r="A69">
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
+    <row r="70" spans="1:3">
       <c r="A70">
         <f t="shared" ref="A70:A102" si="1">A69+1</f>
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:1">
+    <row r="71" spans="1:3">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:1">
+    <row r="72" spans="1:3">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="1:1">
+    <row r="73" spans="1:3">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>71</v>
       </c>
-    </row>
-    <row r="74" spans="1:1">
+      <c r="B73" t="s">
+        <v>5</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
       <c r="A74">
         <f t="shared" si="1"/>
         <v>72</v>
       </c>
-    </row>
-    <row r="75" spans="1:1">
+      <c r="B74" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>73</v>
       </c>
-    </row>
-    <row r="76" spans="1:1">
+      <c r="B75" t="s">
+        <v>5</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
       <c r="A76">
         <f t="shared" si="1"/>
         <v>74</v>
       </c>
-    </row>
-    <row r="77" spans="1:1">
+      <c r="B76" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
       <c r="A77">
         <f t="shared" si="1"/>
         <v>75</v>
       </c>
-    </row>
-    <row r="78" spans="1:1">
+      <c r="B77" t="s">
+        <v>5</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
       <c r="A78">
         <f t="shared" si="1"/>
         <v>76</v>
       </c>
-    </row>
-    <row r="79" spans="1:1">
+      <c r="B78" t="s">
+        <v>5</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>77</v>
       </c>
-    </row>
-    <row r="80" spans="1:1">
+      <c r="B79" t="s">
+        <v>5</v>
+      </c>
+      <c r="C79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>78</v>
+      </c>
+      <c r="B80" t="s">
+        <v>4</v>
+      </c>
+      <c r="C80">
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
         <f t="shared" si="1"/>
         <v>79</v>
+      </c>
+      <c r="B81" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1334,7 +1388,7 @@
     <row r="1" spans="1:4">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1530,193 +1584,265 @@
         <v>130</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:3">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>131</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:3">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>132</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:3">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>133</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:3">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>134</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:3">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>135</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:3">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:3">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:3">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>138</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:3">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>139</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:3">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>140</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:3">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
-    </row>
-    <row r="44" spans="1:1">
+      <c r="B43" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>142</v>
       </c>
-    </row>
-    <row r="45" spans="1:1">
+      <c r="B44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>143</v>
       </c>
-    </row>
-    <row r="46" spans="1:1">
+      <c r="B45" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>144</v>
       </c>
-    </row>
-    <row r="47" spans="1:1">
+      <c r="B46" t="s">
+        <v>4</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>145</v>
       </c>
-    </row>
-    <row r="48" spans="1:1">
+      <c r="B47" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>146</v>
       </c>
-    </row>
-    <row r="49" spans="1:1">
+      <c r="B48" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>147</v>
       </c>
-    </row>
-    <row r="50" spans="1:1">
+      <c r="B49" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>148</v>
       </c>
-    </row>
-    <row r="51" spans="1:1">
+      <c r="B50" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>149</v>
       </c>
-    </row>
-    <row r="52" spans="1:1">
+      <c r="B51" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-    </row>
-    <row r="53" spans="1:1">
+      <c r="B52" t="s">
+        <v>5</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>151</v>
       </c>
-    </row>
-    <row r="54" spans="1:1">
+      <c r="B53" t="s">
+        <v>4</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>152</v>
       </c>
-    </row>
-    <row r="55" spans="1:1">
+      <c r="B54" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>153</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:3">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>154</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:3">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>155</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:3">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>156</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" spans="1:3">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>157</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:3">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>158</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" spans="1:3">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>159</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
+    <row r="62" spans="1:3">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
+    <row r="63" spans="1:3">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>161</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64" spans="1:3">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>162</v>

--- a/toeic-test-v5/trial1_v2.xlsx
+++ b/toeic-test-v5/trial1_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{324571E1-69F5-4B88-BB2B-4416E514F8C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C987D8E-8CA7-4EDC-A269-12D62C45F4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2055" yWindow="540" windowWidth="15225" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2805" yWindow="465" windowWidth="15225" windowHeight="13875" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="12">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -445,14 +445,14 @@
       </c>
       <c r="C3">
         <f>SUM(listening!C3:C12)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D3">
         <v>10</v>
       </c>
       <c r="E3" s="1">
         <f>C3/D3</f>
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="4" spans="2:5">
@@ -523,14 +523,14 @@
       </c>
       <c r="C9">
         <f>SUM(reading!C3:C42)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ref="E9:E11" si="1">C9/D9</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -579,7 +579,7 @@
     <row r="1" spans="1:4">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -600,10 +600,22 @@
       <c r="A3">
         <v>1</v>
       </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4">
         <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -611,47 +623,95 @@
         <f>A4+1</f>
         <v>3</v>
       </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6">
         <f t="shared" ref="A6:A69" si="0">A5+1</f>
         <v>4</v>
       </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1388,7 +1448,7 @@
     <row r="1" spans="1:4">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1408,6 +1468,12 @@
     <row r="3" spans="1:4">
       <c r="A3">
         <v>101</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1415,53 +1481,107 @@
         <f>A3+1</f>
         <v>102</v>
       </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5">
         <f t="shared" ref="A5:A68" si="0">A4+1</f>
         <v>103</v>
       </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>104</v>
       </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>105</v>
       </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>106</v>
       </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>108</v>
       </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>109</v>
       </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>110</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:4">

--- a/toeic-test-v5/trial1_v2.xlsx
+++ b/toeic-test-v5/trial1_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C987D8E-8CA7-4EDC-A269-12D62C45F4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C49AFBEC-DFA6-4A56-832B-E7D56A52BBB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2805" yWindow="465" windowWidth="15225" windowHeight="13875" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5460" yWindow="855" windowWidth="15225" windowHeight="13875" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="12">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -461,14 +461,14 @@
       </c>
       <c r="C4">
         <f>SUM(listening!C13:C42)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D4">
         <v>30</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E6" si="0">C4/D4</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="5" spans="2:5">
@@ -523,14 +523,14 @@
       </c>
       <c r="C9">
         <f>SUM(reading!C3:C42)</f>
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ref="E9:E11" si="1">C9/D9</f>
-        <v>0.2</v>
+        <v>0.42499999999999999</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -579,7 +579,7 @@
     <row r="1" spans="1:4">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>32</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -719,116 +719,176 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
+      <c r="B15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="1:1">
+      <c r="B16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-    </row>
-    <row r="19" spans="1:1">
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-    </row>
-    <row r="20" spans="1:1">
+      <c r="B19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="1:1">
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-    </row>
-    <row r="22" spans="1:1">
+      <c r="B21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="23" spans="1:1">
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:3">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:3">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:3">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:3">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:3">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:3">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:3">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:3">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:3">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -1448,7 +1508,7 @@
     <row r="1" spans="1:4">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>38</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1589,116 +1649,176 @@
         <f t="shared" si="0"/>
         <v>111</v>
       </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>112</v>
       </c>
+      <c r="B14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>113</v>
       </c>
+      <c r="B15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>114</v>
       </c>
-    </row>
-    <row r="17" spans="1:1">
+      <c r="B16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>115</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
+      <c r="B17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>116</v>
       </c>
-    </row>
-    <row r="19" spans="1:1">
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>117</v>
       </c>
-    </row>
-    <row r="20" spans="1:1">
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>118</v>
       </c>
-    </row>
-    <row r="21" spans="1:1">
+      <c r="B20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>119</v>
       </c>
-    </row>
-    <row r="22" spans="1:1">
+      <c r="B21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-    </row>
-    <row r="23" spans="1:1">
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>121</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:3">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>122</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:3">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>123</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:3">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>124</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:3">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>125</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:3">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>126</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:3">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>127</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:3">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:3">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>129</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:3">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>130</v>

--- a/toeic-test-v5/trial1_v2.xlsx
+++ b/toeic-test-v5/trial1_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C49AFBEC-DFA6-4A56-832B-E7D56A52BBB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75BE38F8-25C2-4956-9ADC-6D363DD1BC23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5460" yWindow="855" windowWidth="15225" windowHeight="13875" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="105" yWindow="780" windowWidth="15225" windowHeight="13875" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="12">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -461,14 +461,14 @@
       </c>
       <c r="C4">
         <f>SUM(listening!C13:C42)</f>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D4">
         <v>30</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E6" si="0">C4/D4</f>
-        <v>0.3</v>
+        <v>0.46666666666666667</v>
       </c>
     </row>
     <row r="5" spans="2:5">
@@ -523,14 +523,14 @@
       </c>
       <c r="C9">
         <f>SUM(reading!C3:C42)</f>
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ref="E9:E11" si="1">C9/D9</f>
-        <v>0.42499999999999999</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -579,7 +579,7 @@
     <row r="1" spans="1:4">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -839,59 +839,119 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
+      <c r="B23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
+      <c r="B24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
+      <c r="B26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
+      <c r="B27" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
+      <c r="B28" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
+      <c r="B29" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
+      <c r="B31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:1">
@@ -1508,7 +1568,7 @@
     <row r="1" spans="1:4">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>47</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1769,59 +1829,119 @@
         <f t="shared" si="0"/>
         <v>121</v>
       </c>
+      <c r="B23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>122</v>
       </c>
+      <c r="B24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>123</v>
       </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>124</v>
       </c>
+      <c r="B26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>125</v>
       </c>
+      <c r="B27" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>126</v>
       </c>
+      <c r="B28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>127</v>
       </c>
+      <c r="B29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
+      <c r="B30" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>129</v>
       </c>
+      <c r="B31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>130</v>
+      </c>
+      <c r="B32" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:3">

--- a/toeic-test-v5/trial1_v2.xlsx
+++ b/toeic-test-v5/trial1_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75BE38F8-25C2-4956-9ADC-6D363DD1BC23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81F4A357-767A-4658-9065-4378E4BB595B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="105" yWindow="780" windowWidth="15225" windowHeight="13875" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="525" yWindow="450" windowWidth="14040" windowHeight="14580" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="13">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -96,6 +96,10 @@
     <rPh sb="0" eb="3">
       <t>モンダイスウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　　　　　　　</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -477,14 +481,14 @@
       </c>
       <c r="C5">
         <f>SUM(listening!C43:C72)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D5">
         <v>30</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -555,14 +559,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.39583333333333331</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
   </sheetData>
@@ -579,7 +583,7 @@
     <row r="1" spans="1:4">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1050,100 +1054,124 @@
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:3">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
+    <row r="50" spans="1:3">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
+    <row r="51" spans="1:3">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
+    <row r="52" spans="1:3">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
+    <row r="53" spans="1:3">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54" spans="1:3">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55" spans="1:3">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:3">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:3">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:3">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" spans="1:3">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:3">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" spans="1:3">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-    </row>
-    <row r="62" spans="1:1">
+      <c r="B61" t="s">
+        <v>4</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="63" spans="1:1">
+      <c r="B62" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-    </row>
-    <row r="64" spans="1:1">
+      <c r="B63" t="s">
+        <v>5</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>62</v>
+      </c>
+      <c r="B64" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1151,29 +1179,59 @@
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
+      <c r="B65" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
+      <c r="B66" t="s">
+        <v>5</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
+      <c r="B67" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
+      <c r="B68" t="s">
+        <v>5</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
         <f t="shared" si="0"/>
         <v>67</v>
+      </c>
+      <c r="B69" t="s">
+        <v>5</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1181,17 +1239,35 @@
         <f t="shared" ref="A70:A102" si="1">A69+1</f>
         <v>68</v>
       </c>
+      <c r="B70" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>69</v>
       </c>
+      <c r="B71" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>70</v>
+      </c>
+      <c r="B72" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1562,13 +1638,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A9B22D-A93D-442A-B8E1-1D68266591E9}">
-  <dimension ref="A1:D102"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>55</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2208,100 +2284,169 @@
         <v>162</v>
       </c>
     </row>
-    <row r="65" spans="1:1">
+    <row r="65" spans="1:5">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>163</v>
       </c>
     </row>
-    <row r="66" spans="1:1">
+    <row r="66" spans="1:5">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>164</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
+    <row r="67" spans="1:5">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>165</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
+    <row r="68" spans="1:5">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>166</v>
       </c>
     </row>
-    <row r="69" spans="1:1">
+    <row r="69" spans="1:5">
       <c r="A69">
         <f t="shared" ref="A69:A102" si="1">A68+1</f>
         <v>167</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
+    <row r="70" spans="1:5">
       <c r="A70">
         <f t="shared" si="1"/>
         <v>168</v>
       </c>
-    </row>
-    <row r="71" spans="1:1">
+      <c r="B70" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>169</v>
       </c>
-    </row>
-    <row r="72" spans="1:1">
+      <c r="B71" t="s">
+        <v>4</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>170</v>
       </c>
-    </row>
-    <row r="73" spans="1:1">
+      <c r="B72" t="s">
+        <v>5</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>171</v>
       </c>
-    </row>
-    <row r="74" spans="1:1">
+      <c r="B73" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
       <c r="A74">
         <f t="shared" si="1"/>
         <v>172</v>
       </c>
-    </row>
-    <row r="75" spans="1:1">
+      <c r="B74" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
+      <c r="E74" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>173</v>
       </c>
-    </row>
-    <row r="76" spans="1:1">
+      <c r="B75" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
       <c r="A76">
         <f t="shared" si="1"/>
         <v>174</v>
       </c>
-    </row>
-    <row r="77" spans="1:1">
+      <c r="B76" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
       <c r="A77">
         <f t="shared" si="1"/>
         <v>175</v>
       </c>
-    </row>
-    <row r="78" spans="1:1">
+      <c r="B77" t="s">
+        <v>4</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
       <c r="A78">
         <f t="shared" si="1"/>
         <v>176</v>
       </c>
-    </row>
-    <row r="79" spans="1:1">
+      <c r="B78" t="s">
+        <v>5</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>177</v>
       </c>
-    </row>
-    <row r="80" spans="1:1">
+      <c r="B79" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>178</v>
+      </c>
+      <c r="B80" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80">
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -2309,11 +2454,23 @@
         <f t="shared" si="1"/>
         <v>179</v>
       </c>
+      <c r="B81" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
         <f t="shared" si="1"/>
         <v>180</v>
+      </c>
+      <c r="B82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:3">

--- a/toeic-test-v5/trial1_v2.xlsx
+++ b/toeic-test-v5/trial1_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81F4A357-767A-4658-9065-4378E4BB595B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95530661-8D9D-412D-83F3-12FAB77A5E04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="525" yWindow="450" windowWidth="14040" windowHeight="14580" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15615" yWindow="1155" windowWidth="14040" windowHeight="14580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="13">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -481,14 +481,14 @@
       </c>
       <c r="C5">
         <f>SUM(listening!C43:C72)</f>
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D5">
         <v>30</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
+        <v>0.76666666666666672</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -583,7 +583,7 @@
     <row r="1" spans="1:4">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>56</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -958,100 +958,136 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:3">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:3">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:3">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:3">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:3">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:3">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:3">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:3">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:3">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:3">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:3">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-    </row>
-    <row r="44" spans="1:1">
+      <c r="B43" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-    </row>
-    <row r="45" spans="1:1">
+      <c r="B44" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-    </row>
-    <row r="46" spans="1:1">
+      <c r="B45" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-    </row>
-    <row r="47" spans="1:1">
+      <c r="B46" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-    </row>
-    <row r="48" spans="1:1">
+      <c r="B47" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>46</v>
+      </c>
+      <c r="B48" t="s">
+        <v>4</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1059,71 +1095,143 @@
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
+      <c r="B49" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
+      <c r="B50" t="s">
+        <v>5</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
+      <c r="B51" t="s">
+        <v>5</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
+      <c r="B52" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
+      <c r="B53" t="s">
+        <v>4</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
+      <c r="B54" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
+      <c r="B55" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
+      <c r="B56" t="s">
+        <v>5</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
+      <c r="B57" t="s">
+        <v>4</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
+      <c r="B58" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
+      <c r="B59" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>58</v>
+      </c>
+      <c r="B60" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:3">

--- a/toeic-test-v5/trial1_v2.xlsx
+++ b/toeic-test-v5/trial1_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95530661-8D9D-412D-83F3-12FAB77A5E04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72377E21-27C7-4F3E-BACC-DF26972197AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15615" yWindow="1155" windowWidth="14040" windowHeight="14580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9375" yWindow="900" windowWidth="14040" windowHeight="14580" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="13">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -559,14 +559,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.83333333333333337</v>
       </c>
     </row>
   </sheetData>
@@ -1752,7 +1752,7 @@
     <row r="1" spans="1:4">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2337,47 +2337,95 @@
         <f t="shared" si="0"/>
         <v>153</v>
       </c>
+      <c r="B55" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>154</v>
       </c>
+      <c r="B56" t="s">
+        <v>5</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>155</v>
       </c>
+      <c r="B57" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>156</v>
       </c>
+      <c r="B58" t="s">
+        <v>4</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>157</v>
       </c>
+      <c r="B59" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>158</v>
       </c>
+      <c r="B60" t="s">
+        <v>5</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>159</v>
       </c>
+      <c r="B61" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>160</v>
+      </c>
+      <c r="B62" t="s">
+        <v>4</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:3">

--- a/toeic-test-v5/trial1_v2.xlsx
+++ b/toeic-test-v5/trial1_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72377E21-27C7-4F3E-BACC-DF26972197AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2BC5FCB-9A7A-47B1-B4B0-17F1E189E126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9375" yWindow="900" windowWidth="14040" windowHeight="14580" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="405" yWindow="195" windowWidth="12585" windowHeight="14580" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="13">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -465,14 +465,14 @@
       </c>
       <c r="C4">
         <f>SUM(listening!C13:C42)</f>
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D4">
         <v>30</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E6" si="0">C4/D4</f>
-        <v>0.46666666666666667</v>
+        <v>0.76666666666666672</v>
       </c>
     </row>
     <row r="5" spans="2:5">
@@ -559,14 +559,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.83333333333333337</v>
+        <v>0.95833333333333337</v>
       </c>
     </row>
   </sheetData>
@@ -583,7 +583,7 @@
     <row r="1" spans="1:4">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -963,59 +963,119 @@
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
+      <c r="B33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
+      <c r="B34" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
+      <c r="B35" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
+      <c r="B36" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
+      <c r="B37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
+      <c r="B38" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
+      <c r="B39" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
+      <c r="B40" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
+      <c r="B41" t="s">
+        <v>4</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>40</v>
+      </c>
+      <c r="B42" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1752,7 +1812,7 @@
     <row r="1" spans="1:4">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2133,12 +2193,18 @@
         <f t="shared" si="0"/>
         <v>131</v>
       </c>
+      <c r="B33" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>132</v>
       </c>
+      <c r="B34" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
@@ -2433,41 +2499,83 @@
         <f t="shared" si="0"/>
         <v>161</v>
       </c>
+      <c r="B63" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>162</v>
       </c>
+      <c r="B64" t="s">
+        <v>4</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>163</v>
       </c>
+      <c r="B65" t="s">
+        <v>5</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>164</v>
       </c>
+      <c r="B66" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>165</v>
       </c>
+      <c r="B67" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>166</v>
+      </c>
+      <c r="B68" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69">
         <f t="shared" ref="A69:A102" si="1">A68+1</f>
         <v>167</v>
+      </c>
+      <c r="B69" t="s">
+        <v>5</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:5">

--- a/toeic-test-v5/trial1_v2.xlsx
+++ b/toeic-test-v5/trial1_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2BC5FCB-9A7A-47B1-B4B0-17F1E189E126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C019361F-471C-448A-85D1-B9DD161EBBE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="405" yWindow="195" windowWidth="12585" windowHeight="14580" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="13">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -527,14 +527,14 @@
       </c>
       <c r="C9">
         <f>SUM(reading!C3:C42)</f>
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ref="E9:E11" si="1">C9/D9</f>
-        <v>0.625</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -1812,7 +1812,7 @@
     <row r="1" spans="1:4">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>82</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2196,6 +2196,9 @@
       <c r="B33" t="s">
         <v>4</v>
       </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
@@ -2205,53 +2208,104 @@
       <c r="B34" t="s">
         <v>6</v>
       </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>133</v>
       </c>
+      <c r="B35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>134</v>
       </c>
+      <c r="B36" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>135</v>
       </c>
+      <c r="B37" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
+      <c r="B38" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
+      <c r="B39" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>138</v>
       </c>
+      <c r="B40" t="s">
+        <v>4</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>139</v>
       </c>
+      <c r="B41" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>140</v>
+      </c>
+      <c r="B42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:3">

--- a/toeic-test-v5/trial1_v2.xlsx
+++ b/toeic-test-v5/trial1_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C019361F-471C-448A-85D1-B9DD161EBBE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C8C4856-7D03-4338-A73B-FA425066F061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="405" yWindow="195" windowWidth="12585" windowHeight="14580" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -18,6 +18,10 @@
     <sheet name="reading" sheetId="2" r:id="rId3"/>
     <sheet name="review" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">listening!$A$2:$D$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">reading!$A$2:$E$102</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -28,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="13">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -123,12 +127,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -143,9 +153,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1583,74 +1594,74 @@
       </c>
     </row>
     <row r="85" spans="1:3">
-      <c r="A85">
+      <c r="A85" s="2">
         <f t="shared" si="1"/>
         <v>83</v>
       </c>
-      <c r="B85" t="s">
-        <v>6</v>
-      </c>
-      <c r="C85">
+      <c r="B85" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:3">
-      <c r="A86">
+      <c r="A86" s="2">
         <f t="shared" si="1"/>
         <v>84</v>
       </c>
-      <c r="B86" t="s">
-        <v>6</v>
-      </c>
-      <c r="C86">
+      <c r="B86" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:3">
-      <c r="A87">
+      <c r="A87" s="2">
         <f t="shared" si="1"/>
         <v>85</v>
       </c>
-      <c r="B87" t="s">
-        <v>7</v>
-      </c>
-      <c r="C87">
+      <c r="B87" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88">
+      <c r="A88" s="2">
         <f t="shared" si="1"/>
         <v>86</v>
       </c>
-      <c r="B88" t="s">
-        <v>5</v>
-      </c>
-      <c r="C88">
+      <c r="B88" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C88" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89">
+      <c r="A89" s="2">
         <f t="shared" si="1"/>
         <v>87</v>
       </c>
-      <c r="B89" t="s">
-        <v>7</v>
-      </c>
-      <c r="C89">
+      <c r="B89" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:3">
-      <c r="A90">
+      <c r="A90" s="2">
         <f t="shared" si="1"/>
         <v>88</v>
       </c>
-      <c r="B90" t="s">
-        <v>5</v>
-      </c>
-      <c r="C90">
+      <c r="B90" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C90" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1799,6 +1810,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A2:D2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1806,6 +1818,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A9B22D-A93D-442A-B8E1-1D68266591E9}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:E102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
@@ -1829,7 +1842,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" hidden="1">
       <c r="A3">
         <v>101</v>
       </c>
@@ -1852,7 +1865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" hidden="1">
       <c r="A5">
         <f t="shared" ref="A5:A68" si="0">A4+1</f>
         <v>103</v>
@@ -1864,7 +1877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" hidden="1">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>104</v>
@@ -1876,7 +1889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" hidden="1">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>105</v>
@@ -1888,7 +1901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" hidden="1">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>106</v>
@@ -1900,7 +1913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" hidden="1">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>107</v>
@@ -1912,7 +1925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" hidden="1">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>108</v>
@@ -1936,7 +1949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" hidden="1">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>110</v>
@@ -1948,7 +1961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" hidden="1">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>111</v>
@@ -1960,7 +1973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" hidden="1">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>112</v>
@@ -1972,7 +1985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" hidden="1">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>113</v>
@@ -1984,7 +1997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" hidden="1">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>114</v>
@@ -1996,7 +2009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" hidden="1">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>115</v>
@@ -2020,7 +2033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" hidden="1">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>117</v>
@@ -2032,7 +2045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" hidden="1">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>118</v>
@@ -2044,7 +2057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" hidden="1">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>119</v>
@@ -2056,7 +2069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" hidden="1">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>120</v>
@@ -2068,7 +2081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" hidden="1">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>121</v>
@@ -2080,7 +2093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" hidden="1">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>122</v>
@@ -2092,7 +2105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" hidden="1">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>123</v>
@@ -2116,7 +2129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" hidden="1">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>125</v>
@@ -2128,7 +2141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" hidden="1">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>126</v>
@@ -2140,7 +2153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" hidden="1">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>127</v>
@@ -2152,7 +2165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" hidden="1">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>128</v>
@@ -2164,7 +2177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" hidden="1">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>129</v>
@@ -2188,7 +2201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" hidden="1">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>131</v>
@@ -2200,7 +2213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" hidden="1">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>132</v>
@@ -2212,7 +2225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" hidden="1">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>133</v>
@@ -2236,7 +2249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" hidden="1">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>135</v>
@@ -2248,7 +2261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" hidden="1">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>136</v>
@@ -2260,7 +2273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" hidden="1">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>137</v>
@@ -2296,7 +2309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" hidden="1">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>140</v>
@@ -2308,7 +2321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" hidden="1">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>141</v>
@@ -2320,7 +2333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" hidden="1">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>142</v>
@@ -2332,7 +2345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" hidden="1">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>143</v>
@@ -2344,7 +2357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" hidden="1">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>144</v>
@@ -2356,7 +2369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" hidden="1">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>145</v>
@@ -2380,7 +2393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" hidden="1">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>147</v>
@@ -2392,7 +2405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" hidden="1">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>148</v>
@@ -2404,7 +2417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" hidden="1">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>149</v>
@@ -2416,7 +2429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" hidden="1">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>150</v>
@@ -2428,7 +2441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" hidden="1">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>151</v>
@@ -2440,7 +2453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" hidden="1">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>152</v>
@@ -2452,7 +2465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" hidden="1">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>153</v>
@@ -2464,7 +2477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" hidden="1">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>154</v>
@@ -2476,7 +2489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" hidden="1">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>155</v>
@@ -2488,7 +2501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" hidden="1">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>156</v>
@@ -2500,7 +2513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" hidden="1">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>157</v>
@@ -2512,7 +2525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" hidden="1">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>158</v>
@@ -2524,7 +2537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" hidden="1">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>159</v>
@@ -2536,7 +2549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" hidden="1">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>160</v>
@@ -2560,7 +2573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" hidden="1">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>162</v>
@@ -2572,7 +2585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" hidden="1">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>163</v>
@@ -2584,7 +2597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" hidden="1">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>164</v>
@@ -2596,7 +2609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" hidden="1">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>165</v>
@@ -2608,7 +2621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" hidden="1">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>166</v>
@@ -2620,7 +2633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" hidden="1">
       <c r="A69">
         <f t="shared" ref="A69:A102" si="1">A68+1</f>
         <v>167</v>
@@ -2632,7 +2645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" hidden="1">
       <c r="A70">
         <f t="shared" si="1"/>
         <v>168</v>
@@ -2644,7 +2657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" hidden="1">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>169</v>
@@ -2656,7 +2669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" hidden="1">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>170</v>
@@ -2668,7 +2681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" hidden="1">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>171</v>
@@ -2680,7 +2693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" hidden="1">
       <c r="A74">
         <f t="shared" si="1"/>
         <v>172</v>
@@ -2695,7 +2708,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" hidden="1">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>173</v>
@@ -2707,7 +2720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" hidden="1">
       <c r="A76">
         <f t="shared" si="1"/>
         <v>174</v>
@@ -2719,7 +2732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" hidden="1">
       <c r="A77">
         <f t="shared" si="1"/>
         <v>175</v>
@@ -2731,7 +2744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" hidden="1">
       <c r="A78">
         <f t="shared" si="1"/>
         <v>176</v>
@@ -2743,7 +2756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" hidden="1">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>177</v>
@@ -2755,7 +2768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" hidden="1">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>178</v>
@@ -2767,7 +2780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" hidden="1">
       <c r="A81">
         <f t="shared" si="1"/>
         <v>179</v>
@@ -2779,7 +2792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" hidden="1">
       <c r="A82">
         <f t="shared" si="1"/>
         <v>180</v>
@@ -2791,7 +2804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" hidden="1">
       <c r="A83">
         <f t="shared" si="1"/>
         <v>181</v>
@@ -2803,7 +2816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" hidden="1">
       <c r="A84">
         <f t="shared" si="1"/>
         <v>182</v>
@@ -2815,7 +2828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" hidden="1">
       <c r="A85">
         <f t="shared" si="1"/>
         <v>183</v>
@@ -2827,7 +2840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" hidden="1">
       <c r="A86">
         <f t="shared" si="1"/>
         <v>184</v>
@@ -2839,7 +2852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" hidden="1">
       <c r="A87">
         <f t="shared" si="1"/>
         <v>185</v>
@@ -2851,7 +2864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" hidden="1">
       <c r="A88">
         <f t="shared" si="1"/>
         <v>186</v>
@@ -2863,7 +2876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" hidden="1">
       <c r="A89">
         <f t="shared" si="1"/>
         <v>187</v>
@@ -2875,7 +2888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" hidden="1">
       <c r="A90">
         <f t="shared" si="1"/>
         <v>188</v>
@@ -2887,7 +2900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" hidden="1">
       <c r="A91">
         <f t="shared" si="1"/>
         <v>189</v>
@@ -2899,7 +2912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" hidden="1">
       <c r="A92">
         <f t="shared" si="1"/>
         <v>190</v>
@@ -2923,7 +2936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" hidden="1">
       <c r="A94">
         <f t="shared" si="1"/>
         <v>192</v>
@@ -2935,7 +2948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" hidden="1">
       <c r="A95">
         <f t="shared" si="1"/>
         <v>193</v>
@@ -2947,7 +2960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" hidden="1">
       <c r="A96">
         <f t="shared" si="1"/>
         <v>194</v>
@@ -2959,7 +2972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:3" hidden="1">
       <c r="A97">
         <f t="shared" si="1"/>
         <v>195</v>
@@ -2971,7 +2984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" spans="1:3" hidden="1">
       <c r="A98">
         <f t="shared" si="1"/>
         <v>196</v>
@@ -2983,7 +2996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:3" hidden="1">
       <c r="A99">
         <f t="shared" si="1"/>
         <v>197</v>
@@ -2995,7 +3008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" spans="1:3" hidden="1">
       <c r="A100">
         <f t="shared" si="1"/>
         <v>198</v>
@@ -3007,7 +3020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:3" hidden="1">
       <c r="A101">
         <f t="shared" si="1"/>
         <v>199</v>
@@ -3019,7 +3032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
+    <row r="102" spans="1:3" hidden="1">
       <c r="A102">
         <f t="shared" si="1"/>
         <v>200</v>
@@ -3032,6 +3045,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A2:E102" xr:uid="{86A9B22D-A93D-442A-B8E1-1D68266591E9}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="0"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3039,7 +3059,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6B493C2-9434-41D3-BEAE-B5CD194C20AD}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3054,68 +3074,127 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2">
-        <v>89</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2">
+      <c r="A2" s="2">
+        <v>83</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3">
-        <v>90</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
+      <c r="A3" s="2">
+        <v>84</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4">
-        <v>91</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4">
+      <c r="A4" s="2">
+        <v>85</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5">
-        <v>98</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5">
+      <c r="A5" s="2">
+        <v>86</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6">
-        <v>99</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6">
+      <c r="A6" s="2">
+        <v>87</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7">
-        <v>100</v>
-      </c>
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7">
+      <c r="A7" s="2">
+        <v>88</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="2">
+        <v>191</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <f>A8+1</f>
+        <v>192</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <f t="shared" ref="A10:A12" si="0">A9+1</f>
+        <v>193</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <f t="shared" si="0"/>
+        <v>194</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12">
+        <f t="shared" si="0"/>
+        <v>195</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="2">
         <v>1</v>
       </c>
     </row>

--- a/toeic-test-v5/trial1_v2.xlsx
+++ b/toeic-test-v5/trial1_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C8C4856-7D03-4338-A73B-FA425066F061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE4334B8-D26D-4824-89E9-63A8B01FA58F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="495" yWindow="795" windowWidth="20325" windowHeight="14580" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="13">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -3059,7 +3059,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6B493C2-9434-41D3-BEAE-B5CD194C20AD}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3195,6 +3195,578 @@
         <v>6</v>
       </c>
       <c r="C12" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
+        <v>89</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14">
+        <v>90</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15">
+        <v>91</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16">
+        <v>98</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <v>99</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
+        <v>100</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
+        <v>144</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
+        <v>145</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
+        <v>146</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
+        <v>161</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
+        <v>162</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24">
+        <v>163</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25">
+        <v>164</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
+        <v>165</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27">
+        <v>166</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28">
+        <v>167</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29">
+        <v>62</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30">
+        <v>63</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
+        <v>64</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32">
+        <v>65</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33">
+        <v>66</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34">
+        <v>67</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35">
+        <v>168</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36">
+        <v>169</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C36" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37">
+        <v>170</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38">
+        <v>171</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39">
+        <v>172</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40">
+        <v>173</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41">
+        <v>174</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42">
+        <v>175</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C42" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43">
+        <v>56</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44">
+        <v>57</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C44" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45">
+        <v>58</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46">
+        <v>59</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47">
+        <v>60</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48">
+        <v>61</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C48" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49">
+        <v>153</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50">
+        <v>154</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51">
+        <v>155</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52">
+        <v>156</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53">
+        <v>157</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54">
+        <v>158</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C54" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55">
+        <v>159</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56">
+        <v>160</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C56" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57">
+        <v>161</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C57" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58">
+        <v>162</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C58" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59">
+        <v>47</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60">
+        <v>48</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C60" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61">
+        <v>49</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C61" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62">
+        <v>50</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63">
+        <v>51</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C63" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64">
+        <v>52</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="2">
         <v>1</v>
       </c>
     </row>

--- a/toeic-test-v5/trial1_v2.xlsx
+++ b/toeic-test-v5/trial1_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE4334B8-D26D-4824-89E9-63A8B01FA58F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C001CD-FDA8-4D6F-BB98-38DB911CCB11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="495" yWindow="795" windowWidth="20325" windowHeight="14580" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="13">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -3059,7 +3059,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6B493C2-9434-41D3-BEAE-B5CD194C20AD}">
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3767,6 +3767,105 @@
         <v>7</v>
       </c>
       <c r="C64" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65">
+        <v>47</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C65" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66">
+        <v>48</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C66" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67">
+        <v>49</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68">
+        <v>141</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69">
+        <v>142</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C69" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70">
+        <v>143</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71">
+        <v>144</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C71" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72">
+        <v>145</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73">
+        <v>146</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C73" s="2">
         <v>1</v>
       </c>
     </row>

--- a/toeic-test-v5/trial1_v2.xlsx
+++ b/toeic-test-v5/trial1_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C001CD-FDA8-4D6F-BB98-38DB911CCB11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE06F94-78BF-4428-B4CF-3B802DF69571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="495" yWindow="795" windowWidth="20325" windowHeight="14580" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1275" yWindow="270" windowWidth="18030" windowHeight="14580" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="13">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -153,10 +153,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -3059,7 +3060,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6B493C2-9434-41D3-BEAE-B5CD194C20AD}">
-  <dimension ref="A1:C73"/>
+  <dimension ref="A1:C98"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3866,6 +3867,281 @@
         <v>5</v>
       </c>
       <c r="C73" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74">
+        <v>21</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C74" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75">
+        <v>22</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C75" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76">
+        <v>23</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77">
+        <v>24</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78">
+        <v>25</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C78" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79">
+        <v>26</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C79" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80">
+        <v>27</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C80" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81">
+        <v>28</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C81" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82">
+        <v>29</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C82" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83">
+        <v>30</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" s="3">
+        <v>26</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C84" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" s="3">
+        <v>27</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C85" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" s="3">
+        <v>28</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" s="3">
+        <v>29</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C87" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" s="3">
+        <v>30</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C88" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" s="3">
+        <v>131</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C89" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90">
+        <v>132</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91">
+        <v>133</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92">
+        <v>134</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C92" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93">
+        <v>135</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C93" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94">
+        <v>136</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95">
+        <v>137</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C95" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96">
+        <v>138</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C96" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97">
+        <v>139</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C97" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98">
+        <v>140</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98" s="2">
         <v>1</v>
       </c>
     </row>

--- a/toeic-test-v5/trial1_v2.xlsx
+++ b/toeic-test-v5/trial1_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE06F94-78BF-4428-B4CF-3B802DF69571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01882798-742C-453A-98D5-99F782F468BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1275" yWindow="270" windowWidth="18030" windowHeight="14580" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1905" yWindow="1035" windowWidth="18030" windowHeight="14580" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="15">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -104,6 +104,14 @@
   </si>
   <si>
     <t>　　　　　　　</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>closed</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>and</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3060,7 +3068,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6B493C2-9434-41D3-BEAE-B5CD194C20AD}">
-  <dimension ref="A1:C98"/>
+  <dimension ref="A1:E119"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3981,7 +3989,7 @@
       </c>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84" s="3">
+      <c r="A84">
         <v>26</v>
       </c>
       <c r="B84" s="2" t="s">
@@ -3992,7 +4000,7 @@
       </c>
     </row>
     <row r="85" spans="1:3">
-      <c r="A85" s="3">
+      <c r="A85">
         <v>27</v>
       </c>
       <c r="B85" s="2" t="s">
@@ -4003,7 +4011,7 @@
       </c>
     </row>
     <row r="86" spans="1:3">
-      <c r="A86" s="3">
+      <c r="A86">
         <v>28</v>
       </c>
       <c r="B86" s="2" t="s">
@@ -4014,7 +4022,7 @@
       </c>
     </row>
     <row r="87" spans="1:3">
-      <c r="A87" s="3">
+      <c r="A87">
         <v>29</v>
       </c>
       <c r="B87" s="2" t="s">
@@ -4025,7 +4033,7 @@
       </c>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="3">
+      <c r="A88">
         <v>30</v>
       </c>
       <c r="B88" s="2" t="s">
@@ -4036,7 +4044,7 @@
       </c>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="3">
+      <c r="A89">
         <v>131</v>
       </c>
       <c r="B89" s="2" t="s">
@@ -4123,7 +4131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:5">
       <c r="A97">
         <v>139</v>
       </c>
@@ -4134,7 +4142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" spans="1:5">
       <c r="A98">
         <v>140</v>
       </c>
@@ -4144,6 +4152,235 @@
       <c r="C98" s="2">
         <v>1</v>
       </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="3">
+        <v>21</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C99" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" s="3">
+        <v>22</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C100" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" s="3">
+        <v>23</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" s="3">
+        <v>24</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" s="3">
+        <v>25</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" s="3">
+        <v>26</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C104" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" s="3">
+        <v>27</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C105" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" s="3">
+        <v>28</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C106" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" s="3">
+        <v>29</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C107" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" s="3">
+        <v>30</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C108" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" s="3">
+        <v>101</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C109" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" s="3">
+        <v>102</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C110" s="2">
+        <v>0</v>
+      </c>
+      <c r="E110" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" s="3">
+        <v>103</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C111" s="2">
+        <v>0</v>
+      </c>
+      <c r="E111" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" s="3">
+        <v>104</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C112" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="3">
+        <v>105</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C113" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="3">
+        <v>106</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C114" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" s="3">
+        <v>107</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C115" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" s="3">
+        <v>108</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C116" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" s="3">
+        <v>109</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C117" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" s="3">
+        <v>110</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C118" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/toeic-test-v5/trial1_v2.xlsx
+++ b/toeic-test-v5/trial1_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\toeic-test-v5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01882798-742C-453A-98D5-99F782F468BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E26805D6-65EB-4DDA-B270-2C0A741598C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1035" windowWidth="18030" windowHeight="14580" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11040" yWindow="750" windowWidth="18030" windowHeight="14580" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="15">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -161,11 +161,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -3068,7 +3067,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6B493C2-9434-41D3-BEAE-B5CD194C20AD}">
-  <dimension ref="A1:E119"/>
+  <dimension ref="A1:E128"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4154,7 +4153,7 @@
       </c>
     </row>
     <row r="99" spans="1:5">
-      <c r="A99" s="3">
+      <c r="A99">
         <v>21</v>
       </c>
       <c r="B99" s="2" t="s">
@@ -4165,7 +4164,7 @@
       </c>
     </row>
     <row r="100" spans="1:5">
-      <c r="A100" s="3">
+      <c r="A100">
         <v>22</v>
       </c>
       <c r="B100" s="2" t="s">
@@ -4176,7 +4175,7 @@
       </c>
     </row>
     <row r="101" spans="1:5">
-      <c r="A101" s="3">
+      <c r="A101">
         <v>23</v>
       </c>
       <c r="B101" s="2" t="s">
@@ -4187,7 +4186,7 @@
       </c>
     </row>
     <row r="102" spans="1:5">
-      <c r="A102" s="3">
+      <c r="A102">
         <v>24</v>
       </c>
       <c r="B102" s="2" t="s">
@@ -4198,7 +4197,7 @@
       </c>
     </row>
     <row r="103" spans="1:5">
-      <c r="A103" s="3">
+      <c r="A103">
         <v>25</v>
       </c>
       <c r="B103" s="2" t="s">
@@ -4209,7 +4208,7 @@
       </c>
     </row>
     <row r="104" spans="1:5">
-      <c r="A104" s="3">
+      <c r="A104">
         <v>26</v>
       </c>
       <c r="B104" s="2" t="s">
@@ -4220,7 +4219,7 @@
       </c>
     </row>
     <row r="105" spans="1:5">
-      <c r="A105" s="3">
+      <c r="A105">
         <v>27</v>
       </c>
       <c r="B105" s="2" t="s">
@@ -4231,7 +4230,7 @@
       </c>
     </row>
     <row r="106" spans="1:5">
-      <c r="A106" s="3">
+      <c r="A106">
         <v>28</v>
       </c>
       <c r="B106" s="2" t="s">
@@ -4242,7 +4241,7 @@
       </c>
     </row>
     <row r="107" spans="1:5">
-      <c r="A107" s="3">
+      <c r="A107">
         <v>29</v>
       </c>
       <c r="B107" s="2" t="s">
@@ -4253,7 +4252,7 @@
       </c>
     </row>
     <row r="108" spans="1:5">
-      <c r="A108" s="3">
+      <c r="A108">
         <v>30</v>
       </c>
       <c r="B108" s="2" t="s">
@@ -4264,7 +4263,7 @@
       </c>
     </row>
     <row r="109" spans="1:5">
-      <c r="A109" s="3">
+      <c r="A109">
         <v>101</v>
       </c>
       <c r="B109" s="2" t="s">
@@ -4275,7 +4274,7 @@
       </c>
     </row>
     <row r="110" spans="1:5">
-      <c r="A110" s="3">
+      <c r="A110">
         <v>102</v>
       </c>
       <c r="B110" s="2" t="s">
@@ -4289,7 +4288,7 @@
       </c>
     </row>
     <row r="111" spans="1:5">
-      <c r="A111" s="3">
+      <c r="A111">
         <v>103</v>
       </c>
       <c r="B111" s="2" t="s">
@@ -4303,7 +4302,7 @@
       </c>
     </row>
     <row r="112" spans="1:5">
-      <c r="A112" s="3">
+      <c r="A112">
         <v>104</v>
       </c>
       <c r="B112" s="2" t="s">
@@ -4314,7 +4313,7 @@
       </c>
     </row>
     <row r="113" spans="1:3">
-      <c r="A113" s="3">
+      <c r="A113">
         <v>105</v>
       </c>
       <c r="B113" s="2" t="s">
@@ -4325,7 +4324,7 @@
       </c>
     </row>
     <row r="114" spans="1:3">
-      <c r="A114" s="3">
+      <c r="A114">
         <v>106</v>
       </c>
       <c r="B114" s="2" t="s">
@@ -4336,7 +4335,7 @@
       </c>
     </row>
     <row r="115" spans="1:3">
-      <c r="A115" s="3">
+      <c r="A115">
         <v>107</v>
       </c>
       <c r="B115" s="2" t="s">
@@ -4347,7 +4346,7 @@
       </c>
     </row>
     <row r="116" spans="1:3">
-      <c r="A116" s="3">
+      <c r="A116">
         <v>108</v>
       </c>
       <c r="B116" s="2" t="s">
@@ -4358,7 +4357,7 @@
       </c>
     </row>
     <row r="117" spans="1:3">
-      <c r="A117" s="3">
+      <c r="A117">
         <v>109</v>
       </c>
       <c r="B117" s="2" t="s">
@@ -4369,7 +4368,7 @@
       </c>
     </row>
     <row r="118" spans="1:3">
-      <c r="A118" s="3">
+      <c r="A118">
         <v>110</v>
       </c>
       <c r="B118" s="2" t="s">
@@ -4380,7 +4379,122 @@
       </c>
     </row>
     <row r="119" spans="1:3">
-      <c r="A119" s="3"/>
+      <c r="A119">
+        <v>1</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C119" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120">
+        <v>2</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C120" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121">
+        <f>A120+1</f>
+        <v>3</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C121" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122">
+        <f t="shared" ref="A122:A128" si="1">A121+1</f>
+        <v>4</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C122" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C123" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C124" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C125" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C126" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C127" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="B128" t="s">
+        <v>5</v>
+      </c>
+      <c r="C128">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
